--- a/docs/PRAP_Development_Plan_v1.0.xlsx
+++ b/docs/PRAP_Development_Plan_v1.0.xlsx
@@ -145,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -188,12 +188,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -559,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -624,7 +618,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>FINAL - all review questions closed, issued for Gate 1 approval</t>
+          <t>APPROVED BASELINE - Gate 1 passed 2026-08-01</t>
         </is>
       </c>
     </row>
@@ -667,441 +661,453 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Approved by</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Dan5050-now/project1</t>
+          <t>Dan, 2026-08-01 - Gate 1 passed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>claude/project-resource-assignment-app-1vjdzh</t>
+          <t>Dan5050-now/project1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>claude/project-resource-assignment-app-1vjdzh</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>Supersedes</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>v0.4 (2026-07-31)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Status of this issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>This is the final Step 1 issue. Four review rounds produced 28 questions; all 28 are answered and</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>This is the final Step 1 issue. Four review rounds produced 28 questions; all 28 are answered and</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
           <t>closed, and the review log carries no open item. The plan is submitted for Gate 1 approval.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>What v1.0 changes from v0.4 is small - the last two answers confirmed the design rather than altering</t>
-        </is>
-      </c>
+      <c r="A19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>it. A single close-out is called 'Close-out (final)' (Q-27, as built), and 'Others' projects need no</t>
+          <t>What v1.0 changes from v0.4 is small - the last two answers confirmed the design rather than altering</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>distinguishing: both their period dates AND their period weights are entered by hand (Q-28). That last</t>
+          <t>it. A single close-out is called 'Close-out (final)' (Q-27, as built), and 'Others' projects need no</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t>distinguishing: both their period dates AND their period weights are entered by hand (Q-28). That last</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t>point simplifies the model - PeriodWeightStandard is now a clinical-trial reference table only.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>The plan in one page</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Output        One HTML file, opened by double-click on Windows, offline, no install. One Excel</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Output        One HTML file, opened by double-click on Windows, offline, no install. One Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">                workbook alongside it holds the data and remains the archive of record.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr"/>
-    </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Calculation   load = project period weight x role factor x person weight x month coverage,</t>
-        </is>
-      </c>
+      <c r="A28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">                in FTE where 1.00 FTE = 160 hours per month.</t>
+          <t xml:space="preserve">  Calculation   load = project period weight x role factor x person weight x month coverage,</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Over-allocated above 1.50 FTE in a month; under-allocated below 0.80 FTE for three</t>
+          <t xml:space="preserve">                in FTE where 1.00 FTE = 160 hours per month.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">                Over-allocated above 1.50 FTE in a month; under-allocated below 0.80 FTE for three</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">                or more consecutive months, reported as a run.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr"/>
-    </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Periods       Clinical Trial: five period names derived from milestone dates and month offsets,</t>
-        </is>
-      </c>
+      <c r="A33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">                with Conduct occurring up to twice where an interim DB lock splits it. Weights come</t>
+          <t xml:space="preserve">  Periods       Clinical Trial: five period names derived from milestone dates and month offsets,</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">                from the trial's clinical phase.</t>
+          <t xml:space="preserve">                with Conduct occurring up to twice where an interim DB lock splits it. Weights come</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">                from the trial's clinical phase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">                Others: three periods, dates and weights both entered by hand.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr"/>
-    </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Dashboard     Overall (monthly simulation per project and per person, tables and graphs),</t>
-        </is>
-      </c>
+      <c r="A38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Source data (project), Source data (person). Every field editable, with identifier</t>
+          <t xml:space="preserve">  Dashboard     Overall (monthly simulation per project and per person, tables and graphs),</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">                Source data (project), Source data (person). Every field editable, with identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">                edits cascading to referencing rows.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr"/>
-    </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Build         Five steps, each ending at a review gate. This document closes Step 1.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>What approving this document means</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Gate 1 approval on sheet 12 baselines the 63 requirements on sheet 03 as the contract for Steps 2-5,</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>and confirms the six engineering decisions C-06 to C-11 on sheet 05 that were proposed but never</t>
+          <t>Gate 1 approval on sheet 12 baselines the 63 requirements on sheet 03 as the contract for Steps 2-5,</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>explicitly answered across the review rounds. Those six are listed there with their rationale; if any</t>
+          <t>and confirms the six engineering decisions C-06 to C-11 on sheet 05 that were proposed but never</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
+          <t>explicitly answered across the review rounds. Those six are listed there with their rationale; if any</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
           <t>is wrong, say so at approval rather than after.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>How to read this workbook</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Contents</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>00_Cover</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>Document control, what changed, reading guide.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>01_Version_History</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>Change log for this plan.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>02_Scope</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>Background, objectives, in scope / out of scope.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>03_Requirements</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>Numbered requirement register - the contract for Steps 2-5.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>04_Data_Model</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>Every sheet and column of the single source workbook, with rules.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>05_Resource_Logic</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>The calculation that turns assignments and weights into monthly FTE.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>06_Dashboard_Design</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>The three dashboard tabs: tables, graphs, filters, editing.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>07_Architecture</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>Single-file HTML + Excel-on-disk design and the file-access decision.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>08_WBS_Schedule</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>The five steps broken into tasks, deliverables and review gates.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>09_Version_Control</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>How plan, specification and output files are versioned together.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>10_Risks</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>Risks and assumptions with mitigations.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>11_Open_Questions</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>All 28 questions and their answers. Nothing open.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>12_Review_Log</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>Every change made across the four review rounds, and why. Gate 1 approval block.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>Green = new in v0.2, added from your review answers.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
         <is>
           <t>Orange = changed in v0.2 as a consequence of your review.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="14" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
         <is>
           <t>Yellow = still needs your input.</t>
         </is>
@@ -1591,7 +1597,7 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>FINAL Step 1 baseline. All 28 review questions closed.</t>
+          <t>Step 1 baseline. APPROVED 2026-08-01 by Dan (Gate 1).</t>
         </is>
       </c>
     </row>
@@ -3254,9 +3260,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
     <col width="76" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -4477,23 +4483,31 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>PRAP Development Plan v1.0</t>
         </is>
       </c>
-      <c r="B48" s="22" t="inlineStr"/>
-      <c r="C48" s="22" t="inlineStr"/>
-      <c r="D48" s="23" t="inlineStr">
-        <is>
-          <t>Approved / Approved with comments / Not approved</t>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>APPROVED. Finalise plan v1.0 and proceed to Step 2, beginning with generation of the workbook template and a dummy data file for review.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Step 2 begins only once this gate is recorded as approved. Approving this document baselines the 63 requirements on sheet 03 as the contract for Steps 2-5, and confirms decisions C-06 to C-11 on sheet 05.</t>
+          <t>GATE 1 PASSED. The 63 requirements on sheet 03 are baselined as the contract for Steps 2-5, and decisions C-06 to C-11 on sheet 05 are confirmed. Any change to them now requires a new approval and a version increment, per the rules on sheet 09.</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4868,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Final - for approval</t>
+          <t>APPROVED 2026-08-01 by Dan</t>
         </is>
       </c>
     </row>
@@ -12645,7 +12659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -12952,7 +12966,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>GATE 1 - development plan approved. Approval also confirms decisions C-06..C-11.</t>
+          <t>GATE 1 - development plan approved by Dan, 2026-08-01. Decisions C-06..C-11 confirmed.</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -12962,7 +12976,7 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Pending you</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -12974,22 +12988,22 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Fix the source workbook schema: exact sheet names, column headers, types, value lists.</t>
+          <t>Generate the source workbook template and a dummy data file for review.</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Specification sheet 'Data schema'</t>
+          <t>PRAP_SourceData_Template_v1.0.xlsx + _Dummy_v1.0.xlsx</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Complete - issued for review</t>
         </is>
       </c>
     </row>
@@ -13001,22 +13015,22 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Specify the calculation engine as pseudocode plus the worked example as an acceptance test.</t>
+          <t>Fix the source workbook schema: exact sheet names, column headers, types, value lists.</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Specification sheet 'Calculation'</t>
+          <t>Specification sheet 'Data schema'</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -13028,12 +13042,12 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Specify period derivation per project type, and the over/under-allocation detection.</t>
+          <t>Specify the calculation engine as pseudocode plus the worked example as an acceptance test.</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -13055,17 +13069,17 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Specify import validation rules V-01..V-19 and the findings report.</t>
+          <t>Specify period derivation per project type, and the over/under-allocation detection.</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Specification sheet 'Validation'</t>
+          <t>Specification sheet 'Calculation'</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -13082,17 +13096,17 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Specify each dashboard tab: every table, column, graph, filter and interaction.</t>
+          <t>Specify import validation rules V-01..V-19 and the findings report.</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Specification sheet 'UI spec'</t>
+          <t>Specification sheet 'Validation'</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -13109,17 +13123,17 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Specify on-screen editing, the dirty-state model and export round-tripping.</t>
+          <t>Specify each dashboard tab: every table, column, graph, filter and interaction.</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Specification sheet 'Editing &amp; IO'</t>
+          <t>Specification sheet 'UI spec'</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -13136,17 +13150,17 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Specify the version/compatibility check.</t>
+          <t>Specify on-screen editing, the dirty-state model and export round-tripping.</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Specification sheet 'IO &amp; versioning'</t>
+          <t>Specification sheet 'Editing &amp; IO'</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -13163,17 +13177,17 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Build the requirement-to-specification traceability matrix.</t>
+          <t>Specify the version/compatibility check.</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Specification sheet 'Traceability'</t>
+          <t>Specification sheet 'IO &amp; versioning'</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -13190,17 +13204,17 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>GATE 2 - programming specification approved.</t>
+          <t>Build the requirement-to-specification traceability matrix.</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>PRAP_Programming_Specification_v1.0.xlsx</t>
+          <t>Specification sheet 'Traceability'</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -13212,22 +13226,22 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>High-level UI design: tab structure, page regions, navigation. No code behind it.</t>
+          <t>GATE 2 - programming specification approved.</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Prototype HTML (UI only)</t>
+          <t>PRAP_Programming_Specification_v1.0.xlsx</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
@@ -13244,17 +13258,17 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Requester reviews the high-level component design.</t>
+          <t>High-level UI design: tab structure, page regions, navigation. No code behind it.</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Review comments</t>
+          <t>Prototype HTML (UI only)</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -13271,17 +13285,17 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Final UI design with clear per-component requirements.</t>
+          <t>Requester reviews the high-level component design.</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Prototype HTML v1.0 + component list</t>
+          <t>Review comments</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -13298,17 +13312,17 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>GATE 3 - final design and component list approved. Code generation starts only for approved components.</t>
+          <t>Final UI design with clear per-component requirements.</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Approved component list</t>
+          <t>Prototype HTML v1.0 + component list</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -13320,22 +13334,22 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>IO layer: workbook load, sheet/column mapping, export.</t>
+          <t>GATE 3 - final design and component list approved. Code generation starts only for approved components.</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Application code</t>
+          <t>Approved component list</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -13352,12 +13366,12 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Validation layer: rules V-01..V-19 and the findings report.</t>
+          <t>IO layer: workbook load, sheet/column mapping, export.</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -13379,12 +13393,12 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Model layer, Lists and Config handling.</t>
+          <t>Validation layer: rules V-01..V-19 and the findings report.</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -13406,12 +13420,12 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Edit buffer: on-screen editing, dirty state, per-edit validation.</t>
+          <t>Model layer, Lists and Config handling.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -13433,17 +13447,17 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Calculation engine, verified against the worked example.</t>
+          <t>Edit buffer: on-screen editing, dirty state, per-edit validation.</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Application code + test evidence</t>
+          <t>Application code</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -13460,17 +13474,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Overall tab: tables, graphs, filters, over/under-allocation flagging.</t>
+          <t>Calculation engine, verified against the worked example.</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Application code</t>
+          <t>Application code + test evidence</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -13487,12 +13501,12 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Source data (project) and Source data (person) tabs.</t>
+          <t>Overall tab: tables, graphs, filters, over/under-allocation flagging.</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -13514,17 +13528,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Blank source workbook template with value lists and example rows.</t>
+          <t>Source data (project) and Source data (person) tabs.</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>PRAP_SourceData template</t>
+          <t>Application code</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -13541,17 +13555,17 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Requester reviews output against real data; refinements folded in.</t>
+          <t>Blank source workbook template with value lists and example rows.</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Updated code</t>
+          <t>PRAP_SourceData template</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
@@ -13568,17 +13582,17 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>GATE 4 - application functionally complete.</t>
+          <t>Requester reviews output against real data; refinements folded in.</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>PRAP_Application_v0.9.html</t>
+          <t>Updated code</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -13590,22 +13604,22 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Full pass over the traceability matrix: every Must requirement demonstrated.</t>
+          <t>GATE 4 - application functionally complete.</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Completed traceability matrix</t>
+          <t>PRAP_Application_v0.9.html</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -13622,17 +13636,17 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Test on a clean Windows PC in Edge and Chrome, offline.</t>
+          <t>Full pass over the traceability matrix: every Must requirement demonstrated.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Test evidence</t>
+          <t>Completed traceability matrix</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -13649,17 +13663,17 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Write the user guide: folder layout, how to load, how to maintain source data.</t>
+          <t>Test on a clean Windows PC in Edge and Chrome, offline.</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>User guide</t>
+          <t>Test evidence</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -13676,17 +13690,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Final version alignment across plan, specification and application.</t>
+          <t>Write the user guide: folder layout, how to load, how to maintain source data.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Version alignment table (sheet 09)</t>
+          <t>User guide</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -13703,90 +13717,117 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Final version alignment across plan, specification and application.</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Version alignment table (sheet 09)</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
           <t>G5</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>GATE 5 - release.</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>PRAP_Application_v1.0.html</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Measure</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>Tasks total</t>
         </is>
       </c>
-      <c r="B46" s="8">
-        <f>COUNTA(B5:B42)</f>
+      <c r="B47" s="8">
+        <f>COUNTA(B5:B43)</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="B47" s="10">
-        <f>COUNTIF(E5:E42,"Complete")+COUNTIF(E5:E42,"Complete - issued for review")</f>
+      <c r="B48" s="10">
+        <f>COUNTIF(E5:E43,"Complete")+COUNTIF(E5:E43,"Complete - issued for review")</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>Awaiting the requester</t>
         </is>
       </c>
-      <c r="B48" s="8">
-        <f>COUNTIF(E5:E42,"Pending you")</f>
+      <c r="B49" s="8">
+        <f>COUNTIF(E5:E43,"Pending you")</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="B49" s="10">
-        <f>COUNTIF(E5:E42,"Not started")</f>
+      <c r="B50" s="10">
+        <f>COUNTIF(E5:E43,"Not started")</f>
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="16" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>No duration estimates: the pace is set by review turnaround at each gate, not by build effort.</t>
         </is>
@@ -13794,7 +13835,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,In progress,Pending you,Complete - issued for review,Complete,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
